--- a/cases/cold-chain/published/Cold Chain - Student Workbook.xlsx
+++ b/cases/cold-chain/published/Cold Chain - Student Workbook.xlsx
@@ -665,7 +665,7 @@
         <v>25.4</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>102.21</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="8">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>102.21</v>
+        <v>76.78</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>128</v>
